--- a/schematic/Расчет времени работы.xlsx
+++ b/schematic/Расчет времени работы.xlsx
@@ -43,7 +43,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -52,13 +52,26 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -70,14 +83,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Хороший" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -409,7 +425,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2">
@@ -425,11 +441,11 @@
       <c r="E2">
         <v>2000</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <f>E2/D2</f>
         <v>95.923261390887291</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <f>F2/24</f>
         <v>3.9968025579536373</v>
       </c>
